--- a/data/Team Stats Nacional Asunción.xlsx
+++ b/data/Team Stats Nacional Asunción.xlsx
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>14.0</v>
@@ -2107,10 +2107,10 @@
         <v>70.85</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="Q6" s="0" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R6" s="0" t="n">
         <v>52.0</v>
@@ -2281,7 +2281,7 @@
         <v>100.0</v>
       </c>
       <c r="BV6" s="0" t="n">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="BW6" s="0" t="n">
         <v>11.0</v>
@@ -2383,7 +2383,7 @@
         <v>20.13</v>
       </c>
       <c r="DD6" s="0" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
       </c>
       <c r="DE6" s="0" t="n">
         <v>5.13</v>
@@ -2437,16 +2437,16 @@
         <v>212.0</v>
       </c>
       <c r="M7" s="0" t="n">
-        <v>151.0</v>
+        <v>150.0</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>71.23</v>
+        <v>70.75</v>
       </c>
       <c r="O7" s="0" t="n">
         <v>29.15</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="Q7" s="0" t="n">
         <v>21.0</v>
@@ -2455,10 +2455,10 @@
         <v>40.0</v>
       </c>
       <c r="S7" s="0" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="T7" s="0" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="U7" s="0" t="n">
         <v>31.0</v>
@@ -2467,7 +2467,7 @@
         <v>37.0</v>
       </c>
       <c r="W7" s="0" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="X7" s="0" t="n">
         <v>181.0</v>
@@ -2545,13 +2545,13 @@
         <v>6.0</v>
       </c>
       <c r="AW7" s="0" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="AX7" s="0" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="AY7" s="0" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="AZ7" s="0" t="n">
         <v>1.0</v>
@@ -2656,10 +2656,10 @@
         <v>48.0</v>
       </c>
       <c r="CH7" s="0" t="n">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="CI7" s="0" t="n">
-        <v>81.25</v>
+        <v>79.17</v>
       </c>
       <c r="CJ7" s="0" t="n">
         <v>41.0</v>
@@ -2680,13 +2680,13 @@
         <v>60.0</v>
       </c>
       <c r="CP7" s="0" t="n">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
       <c r="CQ7" s="0" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="CR7" s="0" t="n">
-        <v>62.96</v>
+        <v>62.26</v>
       </c>
       <c r="CS7" s="0" t="n">
         <v>0.0</v>
@@ -2722,7 +2722,7 @@
         <v>18.12</v>
       </c>
       <c r="DD7" s="0" t="n">
-        <v>18.85</v>
+        <v>18.84</v>
       </c>
       <c r="DE7" s="0" t="n">
         <v>10.18</v>
